--- a/demo/samples/practice/01-sales-register.xlsx
+++ b/demo/samples/practice/01-sales-register.xlsx
@@ -420,17 +420,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:I223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,25 +474,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Item Code</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -500,7 +506,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -515,23 +521,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Capacitor 36 MFD (CAP-36UF)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+          <t>CAP-36UF</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Capacitor 36 MFD</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>₹ 210</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>₹ 210</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -540,7 +551,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09-03-2026</t>
+          <t>11-03-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -555,28 +566,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>₹ 16,400</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>16-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -591,28 +607,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4 sq mm Wire 90m Coil (CBL-40SQ)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+          <t>CBL-40SQ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>₹ 3,150</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>₹ 15,750</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04-12-2025</t>
+          <t>06-12-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -627,23 +648,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>₹ 105,000</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -652,7 +678,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21-10-2025</t>
+          <t>23-10-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -667,28 +693,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>12</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>₹ 58,200</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26-04-2026</t>
+          <t>28-04-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -703,23 +734,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cable Gland Set 20mm (ACC-GLND)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+          <t>ACC-GLND</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cable Gland Set 20mm</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>6</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>₹ 180</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>₹ 1,080</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -728,7 +764,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20-10-2025</t>
+          <t>22-10-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -743,28 +779,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>12</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>₹ 21,000</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,28 +820,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Exhaust Fan 250mm (FAN-EXH)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+          <t>FAN-EXH</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Exhaust Fan 250mm</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>6</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>₹ 7,500</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07-12-2025</t>
+          <t>09-12-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -815,28 +861,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>6</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>₹ 10,500</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -851,23 +902,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>20</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>₹ 37,000</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -876,7 +932,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05-04-2026</t>
+          <t>07-04-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -891,23 +947,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1 HP Submersible Pump (PMP-SUB1)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+          <t>PMP-SUB1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1 HP Submersible Pump</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>12</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>₹ 9,600</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>₹ 115,200</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -916,7 +977,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -931,23 +992,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32A MCB Single Pole (SWG-MCB32)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+          <t>SWG-MCB32</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>32A MCB Single Pole</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>₹ 260</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>₹ 260</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -956,7 +1022,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18-07-2026</t>
+          <t>20-07-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -971,23 +1037,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>10</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>₹ 82,000</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -996,7 +1067,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21-01-2026</t>
+          <t>23-01-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1011,23 +1082,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>20</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>₹ 164,000</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -1036,7 +1112,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13-07-2026</t>
+          <t>15-07-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1051,28 +1127,33 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Star Delta Starter 10 HP (STR-SD10)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
+          <t>STR-SD10</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Star Delta Starter 10 HP</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>6</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>₹ 6,400</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>₹ 38,400</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1087,28 +1168,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4 sq mm Wire 90m Coil (CBL-40SQ)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
+          <t>CBL-40SQ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>6</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>₹ 3,150</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>₹ 18,900</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>24-05-2026</t>
+          <t>26-05-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1123,23 +1209,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>12</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>₹ 19,800</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -1148,7 +1239,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>22-07-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1163,28 +1254,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1 HP Submersible Pump (PMP-SUB1)</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
+          <t>PMP-SUB1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1 HP Submersible Pump</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>₹ 9,600</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>₹ 19,200</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20-11-2025</t>
+          <t>22-11-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1199,23 +1295,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>6</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>₹ 570</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -1224,7 +1325,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1239,28 +1340,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Capacitor 60 MFD (CAP-60UF)</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+          <t>CAP-60UF</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Capacitor 60 MFD</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>₹ 680</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26-11-2025</t>
+          <t>28-11-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1275,28 +1381,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>25</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>₹ 121,250</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08-04-2026</t>
+          <t>10-04-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1311,23 +1422,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.5 HP Monoblock Pump (PMP-05HP)</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
+          <t>PMP-05HP</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0.5 HP Monoblock Pump</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>12</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>₹ 3,950</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>₹ 47,400</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -1336,7 +1452,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>17-12-2025</t>
+          <t>19-12-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1351,23 +1467,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>20</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>₹ 290,000</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -1376,7 +1497,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06-10-2025</t>
+          <t>08-10-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1391,23 +1512,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>₹ 52,500</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -1416,7 +1542,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14-01-2026</t>
+          <t>16-01-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1431,23 +1557,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>6</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>₹ 10,500</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -1456,7 +1587,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11-12-2025</t>
+          <t>13-12-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1471,28 +1602,33 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>4</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>₹ 1,360</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1507,23 +1643,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cable Gland Set 20mm (ACC-GLND)</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
+          <t>ACC-GLND</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Cable Gland Set 20mm</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>2</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>₹ 180</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>₹ 360</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -1532,7 +1673,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>03-01-2026</t>
+          <t>05-01-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1547,23 +1688,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>2</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>₹ 3,300</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -1572,7 +1718,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07-04-2026</t>
+          <t>09-04-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1587,23 +1733,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>25</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>₹ 362,500</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -1612,7 +1763,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08-10-2025</t>
+          <t>10-10-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1627,23 +1778,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>1</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -1652,7 +1808,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13-12-2025</t>
+          <t>15-12-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1667,28 +1823,33 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>2</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>₹ 16,400</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20-01-2026</t>
+          <t>22-01-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,23 +1864,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Star Delta Starter 10 HP (STR-SD10)</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
+          <t>STR-SD10</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Star Delta Starter 10 HP</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>4</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>₹ 6,400</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>₹ 25,600</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -1728,7 +1894,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16-11-2025</t>
+          <t>18-11-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1743,28 +1909,33 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>4</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>₹ 7,920</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1779,28 +1950,33 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>₹ 14,550</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1815,23 +1991,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>10</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>₹ 175,000</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -1840,7 +2021,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>02-11-2025</t>
+          <t>04-11-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1855,28 +2036,33 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>4</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>₹ 6,600</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>01-03-2026</t>
+          <t>03-03-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1891,23 +2077,28 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>25</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>₹ 362,500</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -1916,7 +2107,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09-10-2025</t>
+          <t>11-10-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1931,23 +2122,28 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>63A RCCB Four Pole (SWG-RCCB63)</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
+          <t>SWG-RCCB63</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>63A RCCB Four Pole</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
         <v>12</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>₹ 2,850</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>₹ 34,200</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -1956,7 +2152,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07-03-2026</t>
+          <t>09-03-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1971,28 +2167,33 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
         <v>6</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>₹ 11,100</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>28-04-2026</t>
+          <t>30-04-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2007,23 +2208,28 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4 Core Armoured Cable 10m (CBL-ARM4)</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
+          <t>CBL-ARM4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4 Core Armoured Cable 10m</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
         <v>20</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>₹ 4,200</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>₹ 84,000</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -2032,7 +2238,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>29-03-2026</t>
+          <t>31-03-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2047,28 +2253,33 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Exhaust Fan 250mm (FAN-EXH)</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
+          <t>FAN-EXH</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Exhaust Fan 250mm</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
         <v>10</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>₹ 12,500</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20-12-2025</t>
+          <t>22-12-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2083,23 +2294,28 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
         <v>12</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>₹ 1,140</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -2108,7 +2324,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21-07-2026</t>
+          <t>23-07-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2123,28 +2339,33 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
         <v>25</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>₹ 2,375</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13-10-2025</t>
+          <t>15-10-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2159,28 +2380,33 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
         <v>1</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10-01-2026</t>
+          <t>12-01-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2195,23 +2421,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
         <v>2</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>₹ 3,960</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -2220,7 +2451,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>02-02-2026</t>
+          <t>04-02-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2235,28 +2466,33 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
         <v>25</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>₹ 46,250</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2271,28 +2507,33 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
         <v>5</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>₹ 9,250</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07-03-2026</t>
+          <t>09-03-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2307,28 +2548,33 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
         <v>5</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>₹ 9,900</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>28-01-2026</t>
+          <t>30-01-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2343,23 +2589,28 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Exhaust Fan 250mm (FAN-EXH)</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
+          <t>FAN-EXH</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Exhaust Fan 250mm</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
         <v>20</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>₹ 25,000</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -2368,7 +2619,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2383,28 +2634,33 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
         <v>12</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>₹ 19,800</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>28-02-2026</t>
+          <t>02-03-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2419,23 +2675,28 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Exhaust Fan 250mm (FAN-EXH)</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
+          <t>FAN-EXH</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Exhaust Fan 250mm</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
         <v>4</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>₹ 5,000</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -2444,7 +2705,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>02-12-2025</t>
+          <t>04-12-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2459,28 +2720,33 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
         <v>3</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>₹ 52,500</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>14-03-2026</t>
+          <t>16-03-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2495,23 +2761,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Capacitor 36 MFD (CAP-36UF)</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
+          <t>CAP-36UF</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Capacitor 36 MFD</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
         <v>10</v>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>₹ 210</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>₹ 2,100</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -2520,7 +2791,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>17-10-2025</t>
+          <t>19-10-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2535,23 +2806,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
         <v>20</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>₹ 35,000</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -2560,7 +2836,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>30-05-2026</t>
+          <t>01-06-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2575,23 +2851,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
         <v>3</v>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>₹ 5,550</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -2600,7 +2881,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20-02-2026</t>
+          <t>22-02-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2615,23 +2896,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0.5 HP Monoblock Pump (PMP-05HP)</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
+          <t>PMP-05HP</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0.5 HP Monoblock Pump</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
         <v>2</v>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>₹ 3,950</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>₹ 7,900</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -2640,7 +2926,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>29-10-2025</t>
+          <t>31-10-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2655,23 +2941,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4 Core Armoured Cable 10m (CBL-ARM4)</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
+          <t>CBL-ARM4</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>4 Core Armoured Cable 10m</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
         <v>2</v>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>₹ 4,200</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>₹ 8,400</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -2680,7 +2971,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>18-05-2026</t>
+          <t>20-05-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2695,28 +2986,33 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
         <v>2</v>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>₹ 3,500</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>23-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2731,23 +3027,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
         <v>2</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>₹ 9,700</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -2756,7 +3057,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2771,23 +3072,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
         <v>4</v>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>₹ 32,800</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -2796,7 +3102,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16-02-2026</t>
+          <t>18-02-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2811,23 +3117,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
         <v>25</v>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>₹ 362,500</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -2836,7 +3147,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>01-10-2025</t>
+          <t>03-10-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,28 +3162,33 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>63A RCCB Four Pole (SWG-RCCB63)</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
+          <t>SWG-RCCB63</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>63A RCCB Four Pole</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
         <v>3</v>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>₹ 2,850</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>₹ 8,550</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21-02-2026</t>
+          <t>23-02-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2887,28 +3203,33 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4 Core Armoured Cable 10m (CBL-ARM4)</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
+          <t>CBL-ARM4</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>4 Core Armoured Cable 10m</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
         <v>5</v>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>₹ 4,200</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>₹ 21,000</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>13-04-2026</t>
+          <t>15-04-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2923,28 +3244,33 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
         <v>6</v>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>₹ 570</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>05-05-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2959,28 +3285,33 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
         <v>1</v>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>30-01-2026</t>
+          <t>01-02-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2995,23 +3326,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Capacitor 36 MFD (CAP-36UF)</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
+          <t>CAP-36UF</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Capacitor 36 MFD</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
         <v>12</v>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>₹ 210</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>₹ 2,520</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -3020,7 +3356,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>24-12-2025</t>
+          <t>26-12-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3035,28 +3371,33 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
         <v>20</v>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>₹ 33,000</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3071,23 +3412,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
         <v>6</v>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>₹ 11,100</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -3096,7 +3442,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06-12-2025</t>
+          <t>08-12-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3111,23 +3457,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Capacitor 36 MFD (CAP-36UF)</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
+          <t>CAP-36UF</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Capacitor 36 MFD</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
         <v>3</v>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>₹ 210</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>₹ 630</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -3136,7 +3487,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>04-04-2026</t>
+          <t>06-04-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3151,28 +3502,33 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
         <v>10</v>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>₹ 82,000</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3187,28 +3543,33 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Capacitor 60 MFD (CAP-60UF)</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
+          <t>CAP-60UF</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Capacitor 60 MFD</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
         <v>1</v>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>22-02-2026</t>
+          <t>24-02-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3223,23 +3584,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.5 HP Monoblock Pump (PMP-05HP)</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
+          <t>PMP-05HP</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0.5 HP Monoblock Pump</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
         <v>4</v>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>₹ 3,950</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>₹ 15,800</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -3248,7 +3614,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>27-11-2025</t>
+          <t>29-11-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3263,28 +3629,33 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
         <v>5</v>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>₹ 9,250</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>15-12-2025</t>
+          <t>17-12-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3299,23 +3670,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4 Core Armoured Cable 10m (CBL-ARM4)</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
+          <t>CBL-ARM4</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>4 Core Armoured Cable 10m</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
         <v>10</v>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>₹ 4,200</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>₹ 42,000</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -3324,7 +3700,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>12-04-2026</t>
+          <t>14-04-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3339,23 +3715,28 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Capacitor 36 MFD (CAP-36UF)</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
+          <t>CAP-36UF</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Capacitor 36 MFD</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
         <v>10</v>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>₹ 210</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>₹ 2,100</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -3364,7 +3745,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07-11-2025</t>
+          <t>09-11-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3379,23 +3760,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
         <v>25</v>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>₹ 41,250</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -3404,7 +3790,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>30-01-2026</t>
+          <t>01-02-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3419,23 +3805,28 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Star Delta Starter 10 HP (STR-SD10)</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
+          <t>STR-SD10</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Star Delta Starter 10 HP</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
         <v>1</v>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>₹ 6,400</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>₹ 6,400</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -3444,7 +3835,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3459,28 +3850,33 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
         <v>6</v>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>₹ 11,880</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3495,23 +3891,28 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
         <v>3</v>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>₹ 5,250</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -3520,7 +3921,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>26-02-2026</t>
+          <t>28-02-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3535,23 +3936,28 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
         <v>4</v>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>₹ 58,000</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -3560,7 +3966,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>30-11-2025</t>
+          <t>02-12-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3575,28 +3981,33 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Star Delta Starter 10 HP (STR-SD10)</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
+          <t>STR-SD10</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Star Delta Starter 10 HP</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
         <v>1</v>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>₹ 6,400</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>₹ 6,400</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>22-04-2026</t>
+          <t>24-04-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3611,23 +4022,28 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
         <v>2</v>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>₹ 680</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -3636,7 +4052,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20-11-2025</t>
+          <t>22-11-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3651,28 +4067,33 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
         <v>2</v>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>₹ 29,000</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>02-11-2025</t>
+          <t>04-11-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3687,28 +4108,33 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Capacitor 60 MFD (CAP-60UF)</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
+          <t>CAP-60UF</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Capacitor 60 MFD</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
         <v>25</v>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>₹ 8,500</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07-10-2025</t>
+          <t>09-10-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3723,23 +4149,28 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
         <v>10</v>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>₹ 175,000</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -3748,7 +4179,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>19-02-2026</t>
+          <t>21-02-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3763,28 +4194,33 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
         <v>4</v>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>₹ 7,000</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3799,23 +4235,28 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
         <v>2</v>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>₹ 190</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -3824,7 +4265,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>26-02-2026</t>
+          <t>28-02-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3839,23 +4280,28 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Exhaust Fan 250mm (FAN-EXH)</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
+          <t>FAN-EXH</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Exhaust Fan 250mm</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
         <v>10</v>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>₹ 12,500</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -3864,7 +4310,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>25-12-2025</t>
+          <t>27-12-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3879,23 +4325,28 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
         <v>6</v>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>₹ 11,880</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -3904,7 +4355,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>22-04-2026</t>
+          <t>24-04-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3919,23 +4370,28 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0.5 HP Monoblock Pump (PMP-05HP)</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
+          <t>PMP-05HP</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0.5 HP Monoblock Pump</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
         <v>5</v>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>₹ 3,950</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>₹ 19,750</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -3944,7 +4400,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>19-04-2026</t>
+          <t>21-04-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3959,23 +4415,28 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
         <v>12</v>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>₹ 4,080</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -3984,7 +4445,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21-11-2025</t>
+          <t>23-11-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3999,23 +4460,28 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
         <v>10</v>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>₹ 175,000</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -4024,7 +4490,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07-02-2026</t>
+          <t>09-02-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4039,23 +4505,28 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cable Gland Set 20mm (ACC-GLND)</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
+          <t>ACC-GLND</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Cable Gland Set 20mm</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
         <v>5</v>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>₹ 180</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>₹ 900</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -4064,7 +4535,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4079,23 +4550,28 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>4 sq mm Wire 90m Coil (CBL-40SQ)</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
+          <t>CBL-40SQ</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>4 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
         <v>2</v>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>₹ 3,150</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>₹ 6,300</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -4104,7 +4580,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>29-11-2025</t>
+          <t>01-12-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4119,23 +4595,28 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
         <v>6</v>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>₹ 2,040</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -4144,7 +4625,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>14-02-2026</t>
+          <t>16-02-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4159,28 +4640,33 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
         <v>25</v>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>₹ 437,500</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>25-10-2025</t>
+          <t>27-10-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4195,23 +4681,28 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Capacitor 36 MFD (CAP-36UF)</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
+          <t>CAP-36UF</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Capacitor 36 MFD</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
         <v>10</v>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>₹ 210</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>₹ 2,100</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -4220,7 +4711,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>22-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4235,28 +4726,33 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cable Gland Set 20mm (ACC-GLND)</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
+          <t>ACC-GLND</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Cable Gland Set 20mm</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
         <v>12</v>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>₹ 180</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>₹ 2,160</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4271,23 +4767,28 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
         <v>10</v>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -4296,7 +4797,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4311,23 +4812,28 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Cable Gland Set 20mm (ACC-GLND)</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
+          <t>ACC-GLND</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Cable Gland Set 20mm</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
         <v>1</v>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>₹ 180</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>₹ 180</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -4336,7 +4842,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4351,28 +4857,33 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
         <v>20</v>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>₹ 1,900</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>17-02-2026</t>
+          <t>19-02-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4387,23 +4898,28 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
         <v>10</v>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>₹ 145,000</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -4412,7 +4928,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>20-11-2025</t>
+          <t>22-11-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4427,23 +4943,28 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
         <v>2</v>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>₹ 190</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -4452,7 +4973,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4467,28 +4988,33 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
         <v>25</v>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>₹ 437,500</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>29-12-2025</t>
+          <t>31-12-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4503,23 +5029,28 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0.5 HP Monoblock Pump (PMP-05HP)</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
+          <t>PMP-05HP</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0.5 HP Monoblock Pump</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
         <v>4</v>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>₹ 3,950</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>₹ 15,800</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -4528,7 +5059,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>19-12-2025</t>
+          <t>21-12-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4543,23 +5074,28 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Capacitor 60 MFD (CAP-60UF)</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
+          <t>CAP-60UF</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Capacitor 60 MFD</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
         <v>20</v>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>₹ 6,800</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -4568,7 +5104,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>24-01-2026</t>
+          <t>26-01-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4583,23 +5119,28 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
         <v>1</v>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -4608,7 +5149,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>08-04-2026</t>
+          <t>10-04-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4623,28 +5164,33 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
         <v>4</v>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>₹ 32,800</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4659,23 +5205,28 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0.5 HP Monoblock Pump (PMP-05HP)</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
+          <t>PMP-05HP</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0.5 HP Monoblock Pump</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
         <v>10</v>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>₹ 3,950</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>₹ 39,500</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -4684,7 +5235,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>22-04-2026</t>
+          <t>24-04-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4699,28 +5250,33 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
         <v>6</v>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>₹ 11,880</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>10-01-2026</t>
+          <t>12-01-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4735,28 +5291,33 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
         <v>2</v>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>₹ 35,000</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>15-01-2026</t>
+          <t>17-01-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4771,28 +5332,33 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
         <v>5</v>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>₹ 24,250</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10-12-2025</t>
+          <t>12-12-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4807,28 +5373,33 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
         <v>1</v>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>30-11-2025</t>
+          <t>02-12-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4843,23 +5414,28 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Cable Gland Set 20mm (ACC-GLND)</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
+          <t>ACC-GLND</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Cable Gland Set 20mm</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
         <v>5</v>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>₹ 180</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>₹ 900</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -4868,7 +5444,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>07-07-2026</t>
+          <t>09-07-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4883,23 +5459,28 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
         <v>5</v>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>₹ 9,900</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -4908,7 +5489,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4923,23 +5504,28 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
         <v>6</v>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>₹ 2,040</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -4948,7 +5534,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4963,28 +5549,33 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
         <v>4</v>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>₹ 7,000</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>23-10-2025</t>
+          <t>25-10-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4999,23 +5590,28 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
         <v>12</v>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>₹ 4,080</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="I123" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -5024,7 +5620,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>20-09-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5039,23 +5635,28 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
         <v>20</v>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>₹ 164,000</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -5064,7 +5665,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>07-03-2026</t>
+          <t>09-03-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5079,28 +5680,33 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
         <v>1</v>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>22-02-2026</t>
+          <t>24-02-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5115,23 +5721,28 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>4 Core Armoured Cable 10m (CBL-ARM4)</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
+          <t>CBL-ARM4</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>4 Core Armoured Cable 10m</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
         <v>3</v>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>₹ 4,200</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>₹ 12,600</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -5140,7 +5751,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>01-01-2026</t>
+          <t>03-01-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5155,28 +5766,33 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Star Delta Starter 10 HP (STR-SD10)</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
+          <t>STR-SD10</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Star Delta Starter 10 HP</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
         <v>10</v>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>₹ 6,400</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>₹ 64,000</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5191,23 +5807,28 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
         <v>20</v>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>₹ 97,000</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -5216,7 +5837,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>12-01-2026</t>
+          <t>14-01-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5231,23 +5852,28 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>32A MCB Single Pole (SWG-MCB32)</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
+          <t>SWG-MCB32</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>32A MCB Single Pole</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
         <v>20</v>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>₹ 260</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>₹ 5,200</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -5256,7 +5882,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>25-07-2026</t>
+          <t>27-07-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5271,23 +5897,28 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
         <v>3</v>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>₹ 52,500</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -5296,7 +5927,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>23-08-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5311,23 +5942,28 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>63A RCCB Four Pole (SWG-RCCB63)</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
+          <t>SWG-RCCB63</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>63A RCCB Four Pole</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
         <v>4</v>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>₹ 2,850</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>₹ 11,400</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -5336,7 +5972,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5351,28 +5987,33 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.5 HP Monoblock Pump (PMP-05HP)</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
+          <t>PMP-05HP</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0.5 HP Monoblock Pump</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
         <v>10</v>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>₹ 3,950</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>₹ 39,500</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>11-02-2026</t>
+          <t>13-02-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5387,28 +6028,33 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
         <v>12</v>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>₹ 1,140</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>03-05-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5423,23 +6069,28 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
         <v>5</v>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>₹ 24,250</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -5456,17 +6107,18 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
         <is>
           <t>₹ 5,583,570</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>12-04-2026</t>
+          <t>14-04-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5481,23 +6133,28 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>32A MCB Single Pole (SWG-MCB32)</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
+          <t>SWG-MCB32</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>32A MCB Single Pole</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
         <v>25</v>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>₹ 260</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>₹ 6,500</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -5506,7 +6163,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>31-03-2026</t>
+          <t>02-04-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5521,28 +6178,33 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
         <v>25</v>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>₹ 41,250</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>20-12-2025</t>
+          <t>22-12-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5557,28 +6219,33 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
         <v>1</v>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5593,28 +6260,33 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
         <v>6</v>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>₹ 2,040</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>13-02-2026</t>
+          <t>15-02-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5629,23 +6301,28 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
         <v>5</v>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="H141" t="inlineStr">
         <is>
           <t>₹ 9,250</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="I141" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -5654,7 +6331,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>10-01-2026</t>
+          <t>12-01-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5669,28 +6346,33 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
         <v>1</v>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>10-10-2025</t>
+          <t>12-10-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5705,23 +6387,28 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
         <v>6</v>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>₹ 2,040</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -5730,7 +6417,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>28-04-2026</t>
+          <t>30-04-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5745,23 +6432,28 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
         <v>2</v>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>₹ 16,400</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -5770,7 +6462,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>17-02-2026</t>
+          <t>19-02-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5785,23 +6477,28 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
         <v>12</v>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="H145" t="inlineStr">
         <is>
           <t>₹ 98,400</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="I145" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -5810,7 +6507,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>24-04-2026</t>
+          <t>26-04-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5825,28 +6522,33 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
         <v>6</v>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>₹ 87,000</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>01-10-2025</t>
+          <t>03-10-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5861,28 +6563,33 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
         <v>20</v>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>₹ 35,000</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5897,23 +6604,28 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>1 HP Submersible Pump (PMP-SUB1)</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
+          <t>PMP-SUB1</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>1 HP Submersible Pump</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
         <v>4</v>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>₹ 9,600</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>₹ 38,400</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="I148" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -5922,7 +6634,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5937,23 +6649,28 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>63A RCCB Four Pole (SWG-RCCB63)</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
+          <t>SWG-RCCB63</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>63A RCCB Four Pole</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
         <v>5</v>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>₹ 2,850</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="H149" t="inlineStr">
         <is>
           <t>₹ 14,250</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="I149" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -5962,7 +6679,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>06-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5977,28 +6694,33 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E150" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
         <v>25</v>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>₹ 362,500</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6013,23 +6735,28 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Cable Gland Set 20mm (ACC-GLND)</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
+          <t>ACC-GLND</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Cable Gland Set 20mm</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
         <v>25</v>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>₹ 180</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="H151" t="inlineStr">
         <is>
           <t>₹ 4,500</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -6038,7 +6765,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>16-01-2026</t>
+          <t>18-01-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6053,23 +6780,28 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
         <v>10</v>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="H152" t="inlineStr">
         <is>
           <t>₹ 3,400</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -6078,7 +6810,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>21-12-2025</t>
+          <t>23-12-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6093,28 +6825,33 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
         <v>6</v>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="H153" t="inlineStr">
         <is>
           <t>₹ 2,040</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6129,23 +6866,28 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
         <v>3</v>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>₹ 5,550</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="I154" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -6154,7 +6896,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>08-11-2025</t>
+          <t>10-11-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6169,23 +6911,28 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
         <v>10</v>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="H155" t="inlineStr">
         <is>
           <t>₹ 48,500</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="I155" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -6194,7 +6941,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>30-07-2026</t>
+          <t>01-08-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6209,23 +6956,28 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Exhaust Fan 250mm (FAN-EXH)</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
+          <t>FAN-EXH</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Exhaust Fan 250mm</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
         <v>25</v>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>₹ 31,250</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -6234,7 +6986,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6249,23 +7001,28 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>32A MCB Single Pole (SWG-MCB32)</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
+          <t>SWG-MCB32</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>32A MCB Single Pole</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
         <v>5</v>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t>₹ 260</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="H157" t="inlineStr">
         <is>
           <t>₹ 1,300</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
+      <c r="I157" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -6274,7 +7031,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>20-03-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6289,23 +7046,28 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4 Core Armoured Cable 10m (CBL-ARM4)</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
+          <t>CBL-ARM4</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>4 Core Armoured Cable 10m</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
         <v>20</v>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>₹ 4,200</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>₹ 84,000</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="I158" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -6314,7 +7076,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>24-01-2026</t>
+          <t>26-01-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6329,23 +7091,28 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
         <v>2</v>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t>₹ 35,000</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="I159" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -6354,7 +7121,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>06-02-2026</t>
+          <t>08-02-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6369,23 +7136,28 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>5 HP Three Phase Motor (MOT-5HP)</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
+          <t>MOT-5HP</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>5 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
         <v>12</v>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>₹ 17,500</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="H160" t="inlineStr">
         <is>
           <t>₹ 210,000</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="I160" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -6394,7 +7166,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>23-07-2026</t>
+          <t>25-07-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6409,28 +7181,33 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>63A RCCB Four Pole (SWG-RCCB63)</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
+          <t>SWG-RCCB63</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>63A RCCB Four Pole</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
         <v>1</v>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>₹ 2,850</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>₹ 2,850</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>13-11-2025</t>
+          <t>15-11-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6445,23 +7222,28 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E162" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
         <v>6</v>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t>₹ 49,200</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -6470,7 +7252,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6485,28 +7267,33 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
         <v>1</v>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="H163" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>05-01-2026</t>
+          <t>07-01-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6521,28 +7308,33 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>32A MCB Single Pole (SWG-MCB32)</t>
-        </is>
-      </c>
-      <c r="E164" t="n">
+          <t>SWG-MCB32</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>32A MCB Single Pole</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
         <v>12</v>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t>₹ 260</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="H164" t="inlineStr">
         <is>
           <t>₹ 3,120</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>05-04-2026</t>
+          <t>07-04-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6557,28 +7349,33 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Star Delta Starter 10 HP (STR-SD10)</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
+          <t>STR-SD10</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Star Delta Starter 10 HP</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
         <v>5</v>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t>₹ 6,400</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="H165" t="inlineStr">
         <is>
           <t>₹ 32,000</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>25-12-2025</t>
+          <t>27-12-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6593,28 +7390,33 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E166" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
         <v>2</v>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
+      <c r="H166" t="inlineStr">
         <is>
           <t>₹ 3,500</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>05-12-2025</t>
+          <t>07-12-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6629,28 +7431,33 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E167" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
         <v>2</v>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="H167" t="inlineStr">
         <is>
           <t>₹ 3,300</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>04-03-2026</t>
+          <t>06-03-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6665,23 +7472,28 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
         <v>2</v>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="G168" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="H168" t="inlineStr">
         <is>
           <t>₹ 9,700</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="I168" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -6690,7 +7502,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>04-02-2026</t>
+          <t>06-02-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6705,28 +7517,33 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Capacitor 36 MFD (CAP-36UF)</t>
-        </is>
-      </c>
-      <c r="E169" t="n">
+          <t>CAP-36UF</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Capacitor 36 MFD</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
         <v>5</v>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>₹ 210</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="H169" t="inlineStr">
         <is>
           <t>₹ 1,050</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>07-06-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6741,23 +7558,28 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E170" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
         <v>4</v>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="H170" t="inlineStr">
         <is>
           <t>₹ 6,600</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="I170" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -6766,7 +7588,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>03-06-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6781,28 +7603,33 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Cable Gland Set 20mm (ACC-GLND)</t>
-        </is>
-      </c>
-      <c r="E171" t="n">
+          <t>ACC-GLND</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Cable Gland Set 20mm</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
         <v>6</v>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t>₹ 180</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="H171" t="inlineStr">
         <is>
           <t>₹ 1,080</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>24-03-2026</t>
+          <t>26-03-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6817,28 +7644,33 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E172" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
         <v>4</v>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="H172" t="inlineStr">
         <is>
           <t>₹ 7,000</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>11-04-2026</t>
+          <t>13-04-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6853,23 +7685,28 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.5 HP Monoblock Pump (PMP-05HP)</t>
-        </is>
-      </c>
-      <c r="E173" t="n">
+          <t>PMP-05HP</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0.5 HP Monoblock Pump</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
         <v>6</v>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>₹ 3,950</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="H173" t="inlineStr">
         <is>
           <t>₹ 23,700</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
+      <c r="I173" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -6878,7 +7715,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>06-06-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6893,23 +7730,28 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E174" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
         <v>10</v>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="H174" t="inlineStr">
         <is>
           <t>₹ 950</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
+      <c r="I174" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -6918,7 +7760,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>10-04-2026</t>
+          <t>12-04-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6933,28 +7775,33 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Capacitor 60 MFD (CAP-60UF)</t>
-        </is>
-      </c>
-      <c r="E175" t="n">
+          <t>CAP-60UF</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Capacitor 60 MFD</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
         <v>2</v>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="H175" t="inlineStr">
         <is>
           <t>₹ 680</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6969,28 +7816,33 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>32A MCB Single Pole (SWG-MCB32)</t>
-        </is>
-      </c>
-      <c r="E176" t="n">
+          <t>SWG-MCB32</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>32A MCB Single Pole</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
         <v>25</v>
       </c>
-      <c r="F176" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>₹ 260</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
+      <c r="H176" t="inlineStr">
         <is>
           <t>₹ 6,500</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>05-02-2026</t>
+          <t>07-02-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -7005,23 +7857,28 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Cable Gland Set 20mm (ACC-GLND)</t>
-        </is>
-      </c>
-      <c r="E177" t="n">
+          <t>ACC-GLND</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Cable Gland Set 20mm</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
         <v>3</v>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>₹ 180</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="H177" t="inlineStr">
         <is>
           <t>₹ 540</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="I177" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -7030,7 +7887,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>03-02-2026</t>
+          <t>05-02-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -7045,23 +7902,28 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E178" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
         <v>10</v>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="G178" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="H178" t="inlineStr">
         <is>
           <t>₹ 16,500</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="I178" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -7070,7 +7932,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -7085,23 +7947,28 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1 HP Submersible Pump (PMP-SUB1)</t>
-        </is>
-      </c>
-      <c r="E179" t="n">
+          <t>PMP-SUB1</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1 HP Submersible Pump</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
         <v>20</v>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="G179" t="inlineStr">
         <is>
           <t>₹ 9,600</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="H179" t="inlineStr">
         <is>
           <t>₹ 192,000</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
+      <c r="I179" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -7110,7 +7977,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>25-07-2026</t>
+          <t>27-07-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -7125,23 +7992,28 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>32A MCB Single Pole (SWG-MCB32)</t>
-        </is>
-      </c>
-      <c r="E180" t="n">
+          <t>SWG-MCB32</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>32A MCB Single Pole</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
         <v>5</v>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>₹ 260</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="H180" t="inlineStr">
         <is>
           <t>₹ 1,300</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="I180" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -7150,7 +8022,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>14-02-2026</t>
+          <t>16-02-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -7165,28 +8037,33 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E181" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
         <v>12</v>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="G181" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
+      <c r="H181" t="inlineStr">
         <is>
           <t>₹ 22,200</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>22-11-2025</t>
+          <t>24-11-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -7201,28 +8078,33 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E182" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
         <v>4</v>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="G182" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="H182" t="inlineStr">
         <is>
           <t>₹ 7,400</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>25-07-2026</t>
+          <t>27-07-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -7237,28 +8119,33 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E183" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
         <v>6</v>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="G183" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
+      <c r="H183" t="inlineStr">
         <is>
           <t>₹ 11,100</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>11-10-2025</t>
+          <t>13-10-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -7273,28 +8160,33 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E184" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
         <v>1</v>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="H184" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>05-02-2026</t>
+          <t>07-02-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -7309,28 +8201,33 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E185" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
         <v>2</v>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="H185" t="inlineStr">
         <is>
           <t>₹ 680</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>27-11-2025</t>
+          <t>29-11-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -7345,28 +8242,33 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>63A RCCB Four Pole (SWG-RCCB63)</t>
-        </is>
-      </c>
-      <c r="E186" t="n">
+          <t>SWG-RCCB63</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>63A RCCB Four Pole</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
         <v>2</v>
       </c>
-      <c r="F186" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t>₹ 2,850</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
+      <c r="H186" t="inlineStr">
         <is>
           <t>₹ 5,700</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>26-10-2025</t>
+          <t>28-10-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -7381,28 +8283,33 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E187" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
         <v>1</v>
       </c>
-      <c r="F187" t="inlineStr">
+      <c r="G187" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
+      <c r="H187" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>02-12-2025</t>
+          <t>04-12-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -7417,23 +8324,28 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E188" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
         <v>6</v>
       </c>
-      <c r="F188" t="inlineStr">
+      <c r="G188" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
+      <c r="H188" t="inlineStr">
         <is>
           <t>₹ 9,900</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
+      <c r="I188" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -7442,7 +8354,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -7457,28 +8369,33 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E189" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
         <v>6</v>
       </c>
-      <c r="F189" t="inlineStr">
+      <c r="G189" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
+      <c r="H189" t="inlineStr">
         <is>
           <t>₹ 29,100</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>30-07-2026</t>
+          <t>01-08-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7493,28 +8410,33 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>4 sq mm Wire 90m Coil (CBL-40SQ)</t>
-        </is>
-      </c>
-      <c r="E190" t="n">
+          <t>CBL-40SQ</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>4 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
         <v>1</v>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="G190" t="inlineStr">
         <is>
           <t>₹ 3,150</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
+      <c r="H190" t="inlineStr">
         <is>
           <t>₹ 3,150</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>21-01-2026</t>
+          <t>23-01-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -7529,28 +8451,33 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E191" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
         <v>4</v>
       </c>
-      <c r="F191" t="inlineStr">
+      <c r="G191" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
+      <c r="H191" t="inlineStr">
         <is>
           <t>₹ 7,400</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>17-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -7565,23 +8492,28 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>4 sq mm Wire 90m Coil (CBL-40SQ)</t>
-        </is>
-      </c>
-      <c r="E192" t="n">
+          <t>CBL-40SQ</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>4 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
         <v>3</v>
       </c>
-      <c r="F192" t="inlineStr">
+      <c r="G192" t="inlineStr">
         <is>
           <t>₹ 3,150</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
+      <c r="H192" t="inlineStr">
         <is>
           <t>₹ 9,450</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
+      <c r="I192" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -7590,7 +8522,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>16-10-2025</t>
+          <t>18-10-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7605,23 +8537,28 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>32A MCB Single Pole (SWG-MCB32)</t>
-        </is>
-      </c>
-      <c r="E193" t="n">
+          <t>SWG-MCB32</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>32A MCB Single Pole</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
         <v>25</v>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="G193" t="inlineStr">
         <is>
           <t>₹ 260</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
+      <c r="H193" t="inlineStr">
         <is>
           <t>₹ 6,500</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="I193" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -7630,7 +8567,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>14-06-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -7645,23 +8582,28 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E194" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
         <v>1</v>
       </c>
-      <c r="F194" t="inlineStr">
+      <c r="G194" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
+      <c r="H194" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="I194" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -7670,7 +8612,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>27-11-2025</t>
+          <t>29-11-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -7685,23 +8627,28 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Exhaust Fan 250mm (FAN-EXH)</t>
-        </is>
-      </c>
-      <c r="E195" t="n">
+          <t>FAN-EXH</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Exhaust Fan 250mm</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
         <v>25</v>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="G195" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
+      <c r="H195" t="inlineStr">
         <is>
           <t>₹ 31,250</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
+      <c r="I195" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -7710,7 +8657,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>19-02-2026</t>
+          <t>21-02-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7725,28 +8672,33 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>4 sq mm Wire 90m Coil (CBL-40SQ)</t>
-        </is>
-      </c>
-      <c r="E196" t="n">
+          <t>CBL-40SQ</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>4 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
         <v>1</v>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="G196" t="inlineStr">
         <is>
           <t>₹ 3,150</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
+      <c r="H196" t="inlineStr">
         <is>
           <t>₹ 3,150</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>24-03-2026</t>
+          <t>26-03-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7761,28 +8713,33 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Capacitor 36 MFD (CAP-36UF)</t>
-        </is>
-      </c>
-      <c r="E197" t="n">
+          <t>CAP-36UF</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Capacitor 36 MFD</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
         <v>2</v>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="G197" t="inlineStr">
         <is>
           <t>₹ 210</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="H197" t="inlineStr">
         <is>
           <t>₹ 420</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>22-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7797,28 +8754,33 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>32A MCB Single Pole (SWG-MCB32)</t>
-        </is>
-      </c>
-      <c r="E198" t="n">
+          <t>SWG-MCB32</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>32A MCB Single Pole</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
         <v>20</v>
       </c>
-      <c r="F198" t="inlineStr">
+      <c r="G198" t="inlineStr">
         <is>
           <t>₹ 260</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
+      <c r="H198" t="inlineStr">
         <is>
           <t>₹ 5,200</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>22-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7833,23 +8795,28 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E199" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
         <v>12</v>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="G199" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
+      <c r="H199" t="inlineStr">
         <is>
           <t>₹ 21,000</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
+      <c r="I199" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -7858,7 +8825,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7873,28 +8840,33 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Exhaust Fan 250mm (FAN-EXH)</t>
-        </is>
-      </c>
-      <c r="E200" t="n">
+          <t>FAN-EXH</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Exhaust Fan 250mm</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
         <v>1</v>
       </c>
-      <c r="F200" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
+      <c r="H200" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>09-08-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7909,23 +8881,28 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>DOL Starter 3 HP (STR-DOL3)</t>
-        </is>
-      </c>
-      <c r="E201" t="n">
+          <t>STR-DOL3</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>DOL Starter 3 HP</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
         <v>12</v>
       </c>
-      <c r="F201" t="inlineStr">
+      <c r="G201" t="inlineStr">
         <is>
           <t>₹ 1,850</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
+      <c r="H201" t="inlineStr">
         <is>
           <t>₹ 22,200</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
+      <c r="I201" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -7934,7 +8911,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>27-01-2026</t>
+          <t>29-01-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7949,28 +8926,33 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Capacitor 36 MFD (CAP-36UF)</t>
-        </is>
-      </c>
-      <c r="E202" t="n">
+          <t>CAP-36UF</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Capacitor 36 MFD</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
         <v>10</v>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="G202" t="inlineStr">
         <is>
           <t>₹ 210</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="H202" t="inlineStr">
         <is>
           <t>₹ 2,100</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7985,28 +8967,33 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E203" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
         <v>2</v>
       </c>
-      <c r="F203" t="inlineStr">
+      <c r="G203" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="H203" t="inlineStr">
         <is>
           <t>₹ 190</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>20-10-2025</t>
+          <t>22-10-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -8021,23 +9008,28 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.5 HP Monoblock Pump (PMP-05HP)</t>
-        </is>
-      </c>
-      <c r="E204" t="n">
+          <t>PMP-05HP</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>0.5 HP Monoblock Pump</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
         <v>10</v>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="G204" t="inlineStr">
         <is>
           <t>₹ 3,950</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="H204" t="inlineStr">
         <is>
           <t>₹ 39,500</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
+      <c r="I204" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -8046,7 +9038,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>24-11-2025</t>
+          <t>26-11-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -8061,23 +9053,28 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Exhaust Fan 250mm (FAN-EXH)</t>
-        </is>
-      </c>
-      <c r="E205" t="n">
+          <t>FAN-EXH</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Exhaust Fan 250mm</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
         <v>4</v>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="G205" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="H205" t="inlineStr">
         <is>
           <t>₹ 5,000</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
+      <c r="I205" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -8086,7 +9083,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>07-04-2026</t>
+          <t>09-04-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -8101,23 +9098,28 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E206" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
         <v>12</v>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="G206" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="H206" t="inlineStr">
         <is>
           <t>₹ 58,200</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
+      <c r="I206" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -8126,7 +9128,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>24-11-2025</t>
+          <t>26-11-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -8141,28 +9143,33 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>8 Way Distribution Board (SWG-DB8)</t>
-        </is>
-      </c>
-      <c r="E207" t="n">
+          <t>SWG-DB8</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>8 Way Distribution Board</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
         <v>3</v>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="G207" t="inlineStr">
         <is>
           <t>₹ 1,650</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="H207" t="inlineStr">
         <is>
           <t>₹ 4,950</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>03-11-2025</t>
+          <t>05-11-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -8177,28 +9184,33 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Star Delta Starter 10 HP (STR-SD10)</t>
-        </is>
-      </c>
-      <c r="E208" t="n">
+          <t>STR-SD10</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Star Delta Starter 10 HP</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
         <v>3</v>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="G208" t="inlineStr">
         <is>
           <t>₹ 6,400</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="H208" t="inlineStr">
         <is>
           <t>₹ 19,200</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>09-01-2026</t>
+          <t>11-01-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -8213,28 +9225,33 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E209" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
         <v>10</v>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="G209" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="H209" t="inlineStr">
         <is>
           <t>₹ 3,400</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -8249,23 +9266,28 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Ceiling Fan 1200mm (FAN-CEL)</t>
-        </is>
-      </c>
-      <c r="E210" t="n">
+          <t>FAN-CEL</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Ceiling Fan 1200mm</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
         <v>2</v>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="G210" t="inlineStr">
         <is>
           <t>₹ 1,750</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="H210" t="inlineStr">
         <is>
           <t>₹ 3,500</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
+      <c r="I210" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -8274,7 +9296,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>02-02-2026</t>
+          <t>04-02-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -8289,28 +9311,33 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E211" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
         <v>3</v>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="H211" t="inlineStr">
         <is>
           <t>₹ 1,020</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>10-12-2025</t>
+          <t>12-12-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -8325,23 +9352,28 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>1 HP Single Phase Motor (MOT-1HP)</t>
-        </is>
-      </c>
-      <c r="E212" t="n">
+          <t>MOT-1HP</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>1 HP Single Phase Motor</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
         <v>25</v>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="G212" t="inlineStr">
         <is>
           <t>₹ 4,850</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
+      <c r="H212" t="inlineStr">
         <is>
           <t>₹ 121,250</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
+      <c r="I212" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -8350,7 +9382,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>28-04-2026</t>
+          <t>30-04-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -8365,28 +9397,33 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E213" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
         <v>4</v>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="H213" t="inlineStr">
         <is>
           <t>₹ 7,920</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>25-07-2026</t>
+          <t>27-07-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -8401,23 +9438,28 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2 HP Three Phase Motor (MOT-2HP)</t>
-        </is>
-      </c>
-      <c r="E214" t="n">
+          <t>MOT-2HP</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2 HP Three Phase Motor</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
         <v>2</v>
       </c>
-      <c r="F214" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>₹ 8,200</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
+      <c r="H214" t="inlineStr">
         <is>
           <t>₹ 16,400</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
+      <c r="I214" t="inlineStr">
         <is>
           <t>site delivery</t>
         </is>
@@ -8426,7 +9468,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -8441,23 +9483,28 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>0.5 HP Monoblock Pump (PMP-05HP)</t>
-        </is>
-      </c>
-      <c r="E215" t="n">
+          <t>PMP-05HP</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>0.5 HP Monoblock Pump</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
         <v>5</v>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>₹ 3,950</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
+      <c r="H215" t="inlineStr">
         <is>
           <t>₹ 19,750</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
+      <c r="I215" t="inlineStr">
         <is>
           <t>counter sale</t>
         </is>
@@ -8466,7 +9513,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>22-02-2026</t>
+          <t>24-02-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8481,28 +9528,33 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E216" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
         <v>3</v>
       </c>
-      <c r="F216" t="inlineStr">
+      <c r="G216" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="H216" t="inlineStr">
         <is>
           <t>₹ 1,020</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8517,28 +9569,33 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Motor Control Panel 5 HP (PNL-CTRL)</t>
-        </is>
-      </c>
-      <c r="E217" t="n">
+          <t>PNL-CTRL</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Motor Control Panel 5 HP</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
         <v>6</v>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="G217" t="inlineStr">
         <is>
           <t>₹ 14,500</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="H217" t="inlineStr">
         <is>
           <t>₹ 87,000</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>05-10-2025</t>
+          <t>07-10-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -8553,28 +9610,33 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Exhaust Fan 250mm (FAN-EXH)</t>
-        </is>
-      </c>
-      <c r="E218" t="n">
+          <t>FAN-EXH</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Exhaust Fan 250mm</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
         <v>4</v>
       </c>
-      <c r="F218" t="inlineStr">
+      <c r="G218" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
+      <c r="H218" t="inlineStr">
         <is>
           <t>₹ 5,000</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8589,28 +9651,33 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2.5 sq mm Wire 90m Coil (CBL-25SQ)</t>
-        </is>
-      </c>
-      <c r="E219" t="n">
+          <t>CBL-25SQ</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2.5 sq mm Wire 90m Coil</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
         <v>10</v>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="G219" t="inlineStr">
         <is>
           <t>₹ 1,980</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="H219" t="inlineStr">
         <is>
           <t>₹ 19,800</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>19-09-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -8625,23 +9692,28 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20W LED Batten (LMP-LED20)</t>
-        </is>
-      </c>
-      <c r="E220" t="n">
+          <t>LMP-LED20</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>20W LED Batten</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
         <v>10</v>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="G220" t="inlineStr">
         <is>
           <t>₹ 340</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="H220" t="inlineStr">
         <is>
           <t>₹ 3,400</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
+      <c r="I220" t="inlineStr">
         <is>
           <t>urgent</t>
         </is>
@@ -8650,7 +9722,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8665,23 +9737,28 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Exhaust Fan 250mm (FAN-EXH)</t>
-        </is>
-      </c>
-      <c r="E221" t="n">
+          <t>FAN-EXH</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Exhaust Fan 250mm</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
         <v>6</v>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="G221" t="inlineStr">
         <is>
           <t>₹ 1,250</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="H221" t="inlineStr">
         <is>
           <t>₹ 7,500</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="I221" t="inlineStr">
         <is>
           <t>against PO</t>
         </is>
@@ -8690,7 +9767,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>21-04-2026</t>
+          <t>23-04-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -8705,23 +9782,28 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>9W LED Bulb (LMP-LED9)</t>
-        </is>
-      </c>
-      <c r="E222" t="n">
+          <t>LMP-LED9</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>9W LED Bulb</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
         <v>4</v>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="G222" t="inlineStr">
         <is>
           <t>₹ 95</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="H222" t="inlineStr">
         <is>
           <t>₹ 380</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr"/>
@@ -8734,18 +9816,19 @@
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr">
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
         <is>
           <t>₹ 7,729,195</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
